--- a/House_BUS_Subsystem_Tracker.xlsx
+++ b/House_BUS_Subsystem_Tracker.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Seeded</t>
+          <t>Detailed v0.2</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Seeded</t>
+          <t>Detailed v0.1</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Seeded</t>
+          <t>Detailed v0.2</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Seeded</t>
+          <t>Detailed v0.1</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Seeded</t>
+          <t>Detailed v0.1</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Seeded</t>
+          <t>Detailed v0.1</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
